--- a/weather_data.xlsx
+++ b/weather_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -934,6 +934,40 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>09:35:34</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Jaipur</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="E16" t="n">
+        <v>56</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1002</v>
+      </c>
+      <c r="G16" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>overcast clouds</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
